--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-18T20:00:37+00:00</t>
+    <t>2022-02-19T15:25:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-02-19T15:25:03+00:00</t>
+    <t>2022-05-23T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-23T06:59:28+00:00</t>
+    <t>2022-05-24T18:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-05-24T18:54:59+00:00</t>
+    <t>2022-08-17T21:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1400,40 +1400,40 @@
   <dimension ref="A1:AM58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.4375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.44140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="15.6015625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="6.7734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="16.2734375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.2578125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.44140625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="16.27734375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="14.4453125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="81.66015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.265625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="15.26953125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.16796875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="19.03125" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="18.85546875" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="98.375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="22.71484375" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.2109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="10.55078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="13.87109375" customWidth="true" bestFit="true"/>
+    <col min="32" max="32" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="11.0390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="13.875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="36" max="36" width="62.87890625" customWidth="true" bestFit="true"/>
     <col min="37" max="37" width="143.74609375" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-17T21:15:17+00:00</t>
+    <t>2022-09-06T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6302,7 +6302,7 @@
         <v>76</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T15:19:36+00:00</t>
+    <t>2022-09-06T18:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6302,7 +6302,7 @@
         <v>76</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>109</v>
+        <v>182</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T18:47:55+00:00</t>
+    <t>2022-09-06T19:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:01:15+00:00</t>
+    <t>2022-09-06T19:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6302,7 +6302,7 @@
         <v>76</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:02:52+00:00</t>
+    <t>2022-09-06T19:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-06T19:21:39+00:00</t>
+    <t>2022-09-13T07:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -277,267 +277,271 @@
     <t>Y</t>
   </si>
   <si>
+    <t xml:space="preserve">id
+</t>
+  </si>
+  <si>
+    <t>Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+  </si>
+  <si>
+    <t>Resource.id</t>
+  </si>
+  <si>
+    <t>Organization.meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta
+</t>
+  </si>
+  <si>
+    <t>Metadata about the resource</t>
+  </si>
+  <si>
+    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+  </si>
+  <si>
+    <t>Resource.meta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Organization.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Organization.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Organization.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Organization.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Organization.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Organization.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Organization.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifies this organization  across multiple systems</t>
+  </si>
+  <si>
+    <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
+  </si>
+  <si>
+    <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org-1
+</t>
+  </si>
+  <si>
+    <t>XON.10 / XON.3</t>
+  </si>
+  <si>
+    <t>.scopes[Role](classCode=IDENT)</t>
+  </si>
+  <si>
+    <t>./Identifiers</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>EAN-ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-gln-identifier}
+</t>
+  </si>
+  <si>
+    <t>An identifier intended for computation</t>
+  </si>
+  <si>
+    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>SOR-ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-sor-identifier}
+</t>
+  </si>
+  <si>
+    <t>KOMBIT-ORG-ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-kombit-org-identifier}
+</t>
+  </si>
+  <si>
+    <t>Ydernummer</t>
+  </si>
+  <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
-  </si>
-  <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
-  </si>
-  <si>
-    <t>Resource.id</t>
-  </si>
-  <si>
-    <t>Organization.meta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meta
-</t>
-  </si>
-  <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
-  </si>
-  <si>
-    <t>Resource.meta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>Organization.implicitRules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Organization.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Organization.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Organization.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Organization.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Organization.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Organization.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifies this organization  across multiple systems</t>
-  </si>
-  <si>
-    <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
-  </si>
-  <si>
-    <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org-1
-</t>
-  </si>
-  <si>
-    <t>XON.10 / XON.3</t>
-  </si>
-  <si>
-    <t>.scopes[Role](classCode=IDENT)</t>
-  </si>
-  <si>
-    <t>./Identifiers</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>EAN-ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-gln-identifier}
-</t>
-  </si>
-  <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>SOR-ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-sor-identifier}
-</t>
-  </si>
-  <si>
-    <t>KOMBIT-ORG-ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-kombit-org-identifier}
-</t>
-  </si>
-  <si>
-    <t>Ydernummer</t>
-  </si>
-  <si>
-    <t>Organization.identifier.id</t>
   </si>
   <si>
     <t>Unique id for inter-element referencing</t>
@@ -3143,13 +3147,13 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -3200,7 +3204,7 @@
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>77</v>
@@ -3218,7 +3222,7 @@
         <v>76</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3229,7 +3233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3258,7 +3262,7 @@
         <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>134</v>
@@ -3299,10 +3303,10 @@
         <v>76</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC17" t="s" s="2">
         <v>76</v>
@@ -3311,7 +3315,7 @@
         <v>148</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>77</v>
@@ -3329,7 +3333,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3340,7 +3344,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3366,16 +3370,16 @@
         <v>105</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>76</v>
@@ -3400,13 +3404,13 @@
         <v>76</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>76</v>
@@ -3424,7 +3428,7 @@
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>77</v>
@@ -3442,7 +3446,7 @@
         <v>128</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3453,7 +3457,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3476,19 +3480,19 @@
         <v>86</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O19" t="s" s="2">
         <v>76</v>
@@ -3513,13 +3517,13 @@
         <v>76</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>76</v>
@@ -3537,7 +3541,7 @@
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>77</v>
@@ -3552,10 +3556,10 @@
         <v>97</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3566,7 +3570,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3592,29 +3596,29 @@
         <v>99</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>76</v>
@@ -3650,7 +3654,7 @@
         <v>76</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>77</v>
@@ -3665,13 +3669,13 @@
         <v>97</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>76</v>
@@ -3679,7 +3683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3702,16 +3706,16 @@
         <v>86</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -3725,7 +3729,7 @@
         <v>76</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>76</v>
@@ -3761,7 +3765,7 @@
         <v>76</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>77</v>
@@ -3776,13 +3780,13 @@
         <v>97</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -3790,7 +3794,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -3813,13 +3817,13 @@
         <v>86</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3870,7 +3874,7 @@
         <v>76</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>77</v>
@@ -3885,13 +3889,13 @@
         <v>97</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -3899,7 +3903,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -3922,16 +3926,16 @@
         <v>86</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -3981,7 +3985,7 @@
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>77</v>
@@ -3996,13 +4000,13 @@
         <v>97</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4013,7 +4017,7 @@
         <v>142</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>76</v>
@@ -4035,7 +4039,7 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>156</v>
@@ -4126,7 +4130,7 @@
         <v>142</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>76</v>
@@ -4259,13 +4263,13 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4316,7 +4320,7 @@
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>77</v>
@@ -4334,7 +4338,7 @@
         <v>76</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4345,7 +4349,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4374,7 +4378,7 @@
         <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>134</v>
@@ -4415,10 +4419,10 @@
         <v>76</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>76</v>
@@ -4427,7 +4431,7 @@
         <v>148</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>77</v>
@@ -4445,7 +4449,7 @@
         <v>76</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4456,7 +4460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4482,16 +4486,16 @@
         <v>105</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>76</v>
@@ -4516,13 +4520,13 @@
         <v>76</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>76</v>
@@ -4540,7 +4544,7 @@
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>77</v>
@@ -4558,7 +4562,7 @@
         <v>128</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4569,7 +4573,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4592,19 +4596,19 @@
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>76</v>
@@ -4629,13 +4633,13 @@
         <v>76</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>76</v>
@@ -4653,7 +4657,7 @@
         <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>77</v>
@@ -4668,10 +4672,10 @@
         <v>97</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -4682,7 +4686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4708,29 +4712,29 @@
         <v>99</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>76</v>
@@ -4766,7 +4770,7 @@
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>77</v>
@@ -4781,13 +4785,13 @@
         <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>76</v>
@@ -4795,7 +4799,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4818,16 +4822,16 @@
         <v>86</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
@@ -4841,7 +4845,7 @@
         <v>76</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>76</v>
@@ -4853,11 +4857,11 @@
         <v>76</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X31" s="2"/>
       <c r="Y31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>76</v>
@@ -4875,7 +4879,7 @@
         <v>76</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>77</v>
@@ -4890,13 +4894,13 @@
         <v>97</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>76</v>
@@ -4904,7 +4908,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4927,13 +4931,13 @@
         <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4984,7 +4988,7 @@
         <v>76</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>77</v>
@@ -4999,13 +5003,13 @@
         <v>97</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5013,7 +5017,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5036,16 +5040,16 @@
         <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
@@ -5095,7 +5099,7 @@
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>77</v>
@@ -5110,13 +5114,13 @@
         <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5127,7 +5131,7 @@
         <v>142</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>76</v>
@@ -5260,13 +5264,13 @@
         <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -5317,7 +5321,7 @@
         <v>76</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>77</v>
@@ -5335,7 +5339,7 @@
         <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5346,7 +5350,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5375,7 +5379,7 @@
         <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>134</v>
@@ -5416,10 +5420,10 @@
         <v>76</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC36" t="s" s="2">
         <v>76</v>
@@ -5428,7 +5432,7 @@
         <v>148</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>77</v>
@@ -5446,7 +5450,7 @@
         <v>76</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5457,7 +5461,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5483,16 +5487,16 @@
         <v>105</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>76</v>
@@ -5517,13 +5521,13 @@
         <v>76</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>76</v>
@@ -5541,7 +5545,7 @@
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>77</v>
@@ -5559,7 +5563,7 @@
         <v>128</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5570,7 +5574,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -5593,19 +5597,19 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>76</v>
@@ -5630,13 +5634,13 @@
         <v>76</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>76</v>
@@ -5654,7 +5658,7 @@
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>77</v>
@@ -5669,10 +5673,10 @@
         <v>97</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5683,7 +5687,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -5709,29 +5713,29 @@
         <v>99</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>76</v>
@@ -5767,7 +5771,7 @@
         <v>76</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>77</v>
@@ -5782,13 +5786,13 @@
         <v>97</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -5796,7 +5800,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -5819,16 +5823,16 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
@@ -5842,7 +5846,7 @@
         <v>76</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>76</v>
@@ -5878,7 +5882,7 @@
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>77</v>
@@ -5893,13 +5897,13 @@
         <v>97</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -5907,7 +5911,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -5930,13 +5934,13 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5987,7 +5991,7 @@
         <v>76</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>77</v>
@@ -6002,13 +6006,13 @@
         <v>97</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6016,7 +6020,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6039,16 +6043,16 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6098,7 +6102,7 @@
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>77</v>
@@ -6113,13 +6117,13 @@
         <v>97</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6127,7 +6131,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6150,70 +6154,70 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Q43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE43" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Q43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="R43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>77</v>
@@ -6228,21 +6232,21 @@
         <v>97</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6265,19 +6269,19 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>76</v>
@@ -6306,7 +6310,7 @@
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>76</v>
@@ -6324,7 +6328,7 @@
         <v>76</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>77</v>
@@ -6339,21 +6343,21 @@
         <v>97</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6376,19 +6380,19 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>76</v>
@@ -6437,7 +6441,7 @@
         <v>76</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>77</v>
@@ -6452,13 +6456,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6466,7 +6470,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6489,19 +6493,19 @@
         <v>76</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>76</v>
@@ -6550,7 +6554,7 @@
         <v>76</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>77</v>
@@ -6568,7 +6572,7 @@
         <v>76</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6579,7 +6583,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -6602,19 +6606,19 @@
         <v>76</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>76</v>
@@ -6663,7 +6667,7 @@
         <v>76</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>77</v>
@@ -6672,19 +6676,19 @@
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>76</v>
@@ -6692,7 +6696,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -6715,19 +6719,19 @@
         <v>76</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>76</v>
@@ -6776,7 +6780,7 @@
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>77</v>
@@ -6785,19 +6789,19 @@
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>76</v>
@@ -6805,7 +6809,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -6828,17 +6832,17 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>76</v>
@@ -6887,7 +6891,7 @@
         <v>76</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>77</v>
@@ -6902,13 +6906,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>76</v>
@@ -6916,7 +6920,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -6939,19 +6943,19 @@
         <v>76</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>76</v>
@@ -7000,7 +7004,7 @@
         <v>76</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>77</v>
@@ -7018,7 +7022,7 @@
         <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7029,7 +7033,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7052,13 +7056,13 @@
         <v>76</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -7109,7 +7113,7 @@
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>77</v>
@@ -7127,7 +7131,7 @@
         <v>76</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7138,7 +7142,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7167,7 +7171,7 @@
         <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M52" t="s" s="2">
         <v>134</v>
@@ -7220,7 +7224,7 @@
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>77</v>
@@ -7238,7 +7242,7 @@
         <v>76</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7249,11 +7253,11 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7275,10 +7279,10 @@
         <v>131</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>134</v>
@@ -7333,7 +7337,7 @@
         <v>76</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>77</v>
@@ -7362,7 +7366,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7385,17 +7389,17 @@
         <v>76</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>76</v>
@@ -7420,13 +7424,13 @@
         <v>76</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>76</v>
@@ -7444,7 +7448,7 @@
         <v>76</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>77</v>
@@ -7462,7 +7466,7 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7473,7 +7477,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -7496,17 +7500,17 @@
         <v>76</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>76</v>
@@ -7555,7 +7559,7 @@
         <v>76</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>77</v>
@@ -7570,10 +7574,10 @@
         <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7584,7 +7588,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -7607,17 +7611,17 @@
         <v>76</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>76</v>
@@ -7666,7 +7670,7 @@
         <v>76</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>77</v>
@@ -7681,10 +7685,10 @@
         <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7695,7 +7699,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -7718,17 +7722,17 @@
         <v>76</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>76</v>
@@ -7777,7 +7781,7 @@
         <v>76</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>77</v>
@@ -7792,10 +7796,10 @@
         <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7806,7 +7810,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -7829,17 +7833,17 @@
         <v>76</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>76</v>
@@ -7888,7 +7892,7 @@
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>77</v>
@@ -7906,7 +7910,7 @@
         <v>76</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-13T07:22:16+00:00</t>
+    <t>2022-09-17T09:48:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:48:15+00:00</t>
+    <t>2022-09-17T09:59:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T09:59:31+00:00</t>
+    <t>2022-09-17T10:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-17T10:02:16+00:00</t>
+    <t>2022-10-04T11:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="353">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T11:09:51+00:00</t>
+    <t>2022-10-04T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,7 +501,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
+    <t>GLN identifier, [DA] EAN-nummer</t>
   </si>
   <si>
     <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
@@ -527,6 +527,9 @@
 </t>
   </si>
   <si>
+    <t>[DA] SOR-id</t>
+  </si>
+  <si>
     <t>KOMBIT-ORG-ID</t>
   </si>
   <si>
@@ -534,6 +537,9 @@
 </t>
   </si>
   <si>
+    <t>[DA] Organisationsenheds-id som specificeret af FK-ORG</t>
+  </si>
+  <si>
     <t>Ydernummer</t>
   </si>
   <si>
@@ -756,9 +762,15 @@
 </t>
   </si>
   <si>
+    <t>VAT identification number, [DA] CVR-nummer</t>
+  </si>
+  <si>
     <t>Kommunekode</t>
   </si>
   <si>
+    <t>[DA] Kommunekode</t>
+  </si>
+  <si>
     <t>http://hl7.dk/fhir/core/CodeSystem/dk-core-municipality-codes</t>
   </si>
   <si>
@@ -766,6 +778,9 @@
   </si>
   <si>
     <t>Regionskode</t>
+  </si>
+  <si>
+    <t>[DA] Regionskode</t>
   </si>
   <si>
     <t>http://hl7.dk/fhir/core/CodeSystem/dk-core-regional-subdivision-codes</t>
@@ -2813,7 +2828,7 @@
         <v>163</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>157</v>
@@ -2901,7 +2916,7 @@
         <v>142</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>76</v>
@@ -2923,10 +2938,10 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>157</v>
@@ -3014,7 +3029,7 @@
         <v>142</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>76</v>
@@ -3039,7 +3054,7 @@
         <v>143</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>145</v>
@@ -3124,7 +3139,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3147,13 +3162,13 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -3204,7 +3219,7 @@
         <v>76</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>77</v>
@@ -3222,7 +3237,7 @@
         <v>76</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3233,7 +3248,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3262,7 +3277,7 @@
         <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>134</v>
@@ -3303,10 +3318,10 @@
         <v>76</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AC17" t="s" s="2">
         <v>76</v>
@@ -3315,7 +3330,7 @@
         <v>148</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>77</v>
@@ -3333,7 +3348,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3344,7 +3359,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3370,16 +3385,16 @@
         <v>105</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>76</v>
@@ -3404,13 +3419,13 @@
         <v>76</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>76</v>
@@ -3428,7 +3443,7 @@
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>77</v>
@@ -3446,7 +3461,7 @@
         <v>128</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3457,7 +3472,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3480,19 +3495,19 @@
         <v>86</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O19" t="s" s="2">
         <v>76</v>
@@ -3517,13 +3532,13 @@
         <v>76</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>76</v>
@@ -3541,7 +3556,7 @@
         <v>76</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>77</v>
@@ -3556,10 +3571,10 @@
         <v>97</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>76</v>
@@ -3570,7 +3585,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -3596,29 +3611,29 @@
         <v>99</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>76</v>
@@ -3654,7 +3669,7 @@
         <v>76</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>77</v>
@@ -3669,13 +3684,13 @@
         <v>97</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>76</v>
@@ -3683,7 +3698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -3706,16 +3721,16 @@
         <v>86</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -3729,7 +3744,7 @@
         <v>76</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>76</v>
@@ -3765,7 +3780,7 @@
         <v>76</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>77</v>
@@ -3780,13 +3795,13 @@
         <v>97</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -3794,7 +3809,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -3817,13 +3832,13 @@
         <v>86</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -3874,7 +3889,7 @@
         <v>76</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>77</v>
@@ -3889,13 +3904,13 @@
         <v>97</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>76</v>
@@ -3903,7 +3918,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -3926,16 +3941,16 @@
         <v>86</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
@@ -3985,7 +4000,7 @@
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>77</v>
@@ -4000,13 +4015,13 @@
         <v>97</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
@@ -4017,7 +4032,7 @@
         <v>142</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>76</v>
@@ -4039,10 +4054,10 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>157</v>
@@ -4130,7 +4145,7 @@
         <v>142</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>76</v>
@@ -4155,7 +4170,7 @@
         <v>143</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>145</v>
@@ -4240,7 +4255,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4263,13 +4278,13 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4320,7 +4335,7 @@
         <v>76</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>77</v>
@@ -4338,7 +4353,7 @@
         <v>76</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
@@ -4349,7 +4364,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4378,7 +4393,7 @@
         <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>134</v>
@@ -4419,10 +4434,10 @@
         <v>76</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>76</v>
@@ -4431,7 +4446,7 @@
         <v>148</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>77</v>
@@ -4449,7 +4464,7 @@
         <v>76</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4460,7 +4475,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4486,16 +4501,16 @@
         <v>105</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>76</v>
@@ -4520,13 +4535,13 @@
         <v>76</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>76</v>
@@ -4544,7 +4559,7 @@
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>77</v>
@@ -4562,7 +4577,7 @@
         <v>128</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
@@ -4573,7 +4588,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -4596,19 +4611,19 @@
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>76</v>
@@ -4633,13 +4648,13 @@
         <v>76</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>76</v>
@@ -4657,7 +4672,7 @@
         <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>77</v>
@@ -4672,10 +4687,10 @@
         <v>97</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -4686,7 +4701,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -4712,29 +4727,29 @@
         <v>99</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>76</v>
@@ -4770,7 +4785,7 @@
         <v>76</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>77</v>
@@ -4785,13 +4800,13 @@
         <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>76</v>
@@ -4799,7 +4814,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -4822,16 +4837,16 @@
         <v>86</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
@@ -4845,7 +4860,7 @@
         <v>76</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>76</v>
@@ -4857,11 +4872,11 @@
         <v>76</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="X31" s="2"/>
       <c r="Y31" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>76</v>
@@ -4879,7 +4894,7 @@
         <v>76</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>77</v>
@@ -4894,13 +4909,13 @@
         <v>97</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>76</v>
@@ -4908,7 +4923,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -4931,13 +4946,13 @@
         <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -4988,7 +5003,7 @@
         <v>76</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>77</v>
@@ -5003,13 +5018,13 @@
         <v>97</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5017,7 +5032,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5040,16 +5055,16 @@
         <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
@@ -5099,7 +5114,7 @@
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>77</v>
@@ -5114,13 +5129,13 @@
         <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>76</v>
@@ -5131,7 +5146,7 @@
         <v>142</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>76</v>
@@ -5156,7 +5171,7 @@
         <v>143</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>144</v>
+        <v>246</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>145</v>
@@ -5241,7 +5256,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5264,13 +5279,13 @@
         <v>76</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -5321,7 +5336,7 @@
         <v>76</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>77</v>
@@ -5339,7 +5354,7 @@
         <v>76</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5350,7 +5365,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5379,7 +5394,7 @@
         <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>134</v>
@@ -5420,10 +5435,10 @@
         <v>76</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AC36" t="s" s="2">
         <v>76</v>
@@ -5432,7 +5447,7 @@
         <v>148</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>77</v>
@@ -5450,7 +5465,7 @@
         <v>76</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
@@ -5461,7 +5476,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5487,16 +5502,16 @@
         <v>105</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>76</v>
@@ -5521,13 +5536,13 @@
         <v>76</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>76</v>
@@ -5545,7 +5560,7 @@
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>77</v>
@@ -5563,7 +5578,7 @@
         <v>128</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5574,7 +5589,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -5597,19 +5612,19 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>76</v>
@@ -5634,13 +5649,13 @@
         <v>76</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>76</v>
@@ -5658,7 +5673,7 @@
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>77</v>
@@ -5673,10 +5688,10 @@
         <v>97</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5687,7 +5702,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -5713,29 +5728,29 @@
         <v>99</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="R39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>76</v>
@@ -5771,7 +5786,7 @@
         <v>76</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>77</v>
@@ -5786,13 +5801,13 @@
         <v>97</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>76</v>
@@ -5800,7 +5815,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -5823,16 +5838,16 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
@@ -5846,7 +5861,7 @@
         <v>76</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>76</v>
@@ -5882,7 +5897,7 @@
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>77</v>
@@ -5897,13 +5912,13 @@
         <v>97</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>76</v>
@@ -5911,7 +5926,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -5934,13 +5949,13 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5991,7 +6006,7 @@
         <v>76</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>77</v>
@@ -6006,13 +6021,13 @@
         <v>97</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>76</v>
@@ -6020,7 +6035,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6043,16 +6058,16 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6102,7 +6117,7 @@
         <v>76</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>77</v>
@@ -6117,13 +6132,13 @@
         <v>97</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6131,7 +6146,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6154,70 +6169,70 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="N43" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="Q43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE43" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Q43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="R43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>77</v>
@@ -6232,21 +6247,21 @@
         <v>97</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6269,19 +6284,19 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>76</v>
@@ -6310,25 +6325,25 @@
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE44" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>77</v>
@@ -6343,21 +6358,21 @@
         <v>97</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6380,19 +6395,19 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>76</v>
@@ -6441,7 +6456,7 @@
         <v>76</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>77</v>
@@ -6456,13 +6471,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6470,7 +6485,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6493,19 +6508,19 @@
         <v>76</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="O46" t="s" s="2">
         <v>76</v>
@@ -6554,7 +6569,7 @@
         <v>76</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>77</v>
@@ -6572,7 +6587,7 @@
         <v>76</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
@@ -6583,7 +6598,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -6606,19 +6621,19 @@
         <v>76</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>76</v>
@@ -6667,7 +6682,7 @@
         <v>76</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>77</v>
@@ -6676,19 +6691,19 @@
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>76</v>
@@ -6696,7 +6711,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -6719,19 +6734,19 @@
         <v>76</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="O48" t="s" s="2">
         <v>76</v>
@@ -6780,7 +6795,7 @@
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>77</v>
@@ -6789,19 +6804,19 @@
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>76</v>
@@ -6809,7 +6824,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -6832,17 +6847,17 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>76</v>
@@ -6891,7 +6906,7 @@
         <v>76</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>77</v>
@@ -6906,13 +6921,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>76</v>
@@ -6920,7 +6935,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -6943,19 +6958,19 @@
         <v>76</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>76</v>
@@ -7004,7 +7019,7 @@
         <v>76</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>77</v>
@@ -7022,7 +7037,7 @@
         <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7033,7 +7048,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7056,13 +7071,13 @@
         <v>76</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -7113,7 +7128,7 @@
         <v>76</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>77</v>
@@ -7131,7 +7146,7 @@
         <v>76</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7142,7 +7157,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7171,7 +7186,7 @@
         <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M52" t="s" s="2">
         <v>134</v>
@@ -7224,7 +7239,7 @@
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>77</v>
@@ -7242,7 +7257,7 @@
         <v>76</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7253,11 +7268,11 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7279,10 +7294,10 @@
         <v>131</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>134</v>
@@ -7337,7 +7352,7 @@
         <v>76</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>77</v>
@@ -7366,7 +7381,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7389,17 +7404,17 @@
         <v>76</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>76</v>
@@ -7424,31 +7439,31 @@
         <v>76</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="Y54" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE54" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>77</v>
@@ -7466,7 +7481,7 @@
         <v>76</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7477,7 +7492,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -7500,17 +7515,17 @@
         <v>76</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>76</v>
@@ -7559,7 +7574,7 @@
         <v>76</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>77</v>
@@ -7574,10 +7589,10 @@
         <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7588,7 +7603,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -7611,17 +7626,17 @@
         <v>76</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>76</v>
@@ -7670,7 +7685,7 @@
         <v>76</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>77</v>
@@ -7685,10 +7700,10 @@
         <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>76</v>
@@ -7699,7 +7714,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -7722,17 +7737,17 @@
         <v>76</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>76</v>
@@ -7781,7 +7796,7 @@
         <v>76</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>77</v>
@@ -7796,10 +7811,10 @@
         <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7810,7 +7825,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -7833,17 +7848,17 @@
         <v>76</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>76</v>
@@ -7892,7 +7907,7 @@
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>77</v>
@@ -7910,7 +7925,7 @@
         <v>76</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T14:18:04+00:00</t>
+    <t>2022-10-04T19:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T19:52:49+00:00</t>
+    <t>2022-10-04T20:54:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-04T20:54:27+00:00</t>
+    <t>2022-10-11T09:25:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,10 +256,6 @@
   </si>
   <si>
     <t>A formally or informally recognized grouping of people or organizations formed for the purpose of achieving some form of collective action.  Includes companies, institutions, corporations, departments, community groups, healthcare practice groups, payer/insurer, etc.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}dk-core-organization-mandatory-identifier:Minimum one identifier shall be of type SOR-ID, KOMBIT-ORG-ID or CVR-ID {identifier.where(system='urn:oid:1.2.208.176.1.1' or system='https://kombit.dk/sts/organisation' or system='urn:oid:2.16.840.1.113883.2.24.1.1').exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -541,6 +537,9 @@
   </si>
   <si>
     <t>Ydernummer</t>
+  </si>
+  <si>
+    <t>[DA] Ydernummer</t>
   </si>
   <si>
     <t>Organization.identifier.id</t>
@@ -1673,13 +1672,13 @@
         <v>76</v>
       </c>
       <c r="AI2" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AJ2" t="s" s="2">
+      <c r="AK2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AL2" t="s" s="2">
         <v>30</v>
@@ -1690,7 +1689,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -1701,28 +1700,28 @@
         <v>77</v>
       </c>
       <c r="F3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I3" t="s" s="2">
+      <c r="J3" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" t="s" s="2">
@@ -1772,13 +1771,13 @@
         <v>76</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>76</v>
@@ -1801,7 +1800,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -1812,25 +1811,25 @@
         <v>77</v>
       </c>
       <c r="F4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I4" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="K4" t="s" s="2">
+      <c r="L4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1881,19 +1880,19 @@
         <v>76</v>
       </c>
       <c r="AE4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AF4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>76</v>
@@ -1910,7 +1909,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -1921,28 +1920,28 @@
         <v>77</v>
       </c>
       <c r="F5" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H5" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="K5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="K5" t="s" s="2">
+      <c r="L5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" t="s" s="2">
@@ -1992,19 +1991,19 @@
         <v>76</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>76</v>
@@ -2021,7 +2020,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2032,7 +2031,7 @@
         <v>77</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>76</v>
@@ -2044,16 +2043,16 @@
         <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
@@ -2079,43 +2078,43 @@
         <v>76</v>
       </c>
       <c r="W6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="X6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="X6" t="s" s="2">
+      <c r="Y6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>112</v>
-      </c>
       <c r="AF6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>76</v>
@@ -2132,18 +2131,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>76</v>
@@ -2155,16 +2154,16 @@
         <v>76</v>
       </c>
       <c r="J7" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="K7" t="s" s="2">
+      <c r="L7" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
@@ -2214,25 +2213,25 @@
         <v>76</v>
       </c>
       <c r="AE7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -2243,11 +2242,11 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -2266,16 +2265,16 @@
         <v>76</v>
       </c>
       <c r="J8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="K8" t="s" s="2">
+      <c r="L8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" t="s" s="2">
@@ -2325,7 +2324,7 @@
         <v>76</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AF8" t="s" s="2">
         <v>77</v>
@@ -2343,7 +2342,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2354,11 +2353,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -2377,16 +2376,16 @@
         <v>76</v>
       </c>
       <c r="J9" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="K9" t="s" s="2">
+      <c r="L9" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" t="s" s="2">
@@ -2436,7 +2435,7 @@
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>77</v>
@@ -2448,13 +2447,13 @@
         <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2465,11 +2464,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
@@ -2482,25 +2481,25 @@
         <v>76</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
         <v>76</v>
@@ -2549,7 +2548,7 @@
         <v>76</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="s" s="2">
         <v>77</v>
@@ -2561,13 +2560,13 @@
         <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>76</v>
@@ -2578,7 +2577,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2586,7 +2585,7 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>78</v>
@@ -2598,20 +2597,20 @@
         <v>76</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="K11" t="s" s="2">
+      <c r="L11" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O11" t="s" s="2">
         <v>76</v>
@@ -2648,17 +2647,17 @@
         <v>76</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AB11" s="2"/>
       <c r="AC11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>77</v>
@@ -2667,30 +2666,30 @@
         <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AI11" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
+      <c r="AK11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>76</v>
@@ -2700,7 +2699,7 @@
         <v>77</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>76</v>
@@ -2712,17 +2711,17 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="K12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="K12" t="s" s="2">
+      <c r="L12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O12" t="s" s="2">
         <v>76</v>
@@ -2771,7 +2770,7 @@
         <v>76</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>77</v>
@@ -2780,19 +2779,19 @@
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AI12" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
+      <c r="AK12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AL12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>76</v>
@@ -2800,10 +2799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>76</v>
@@ -2813,7 +2812,7 @@
         <v>77</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>76</v>
@@ -2825,17 +2824,17 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="K13" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O13" t="s" s="2">
         <v>76</v>
@@ -2884,7 +2883,7 @@
         <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>77</v>
@@ -2893,19 +2892,19 @@
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AI13" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
+      <c r="AK13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>76</v>
@@ -2913,10 +2912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>76</v>
@@ -2926,7 +2925,7 @@
         <v>77</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>76</v>
@@ -2938,17 +2937,17 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="K14" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="L14" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O14" t="s" s="2">
         <v>76</v>
@@ -2997,7 +2996,7 @@
         <v>76</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>77</v>
@@ -3006,19 +3005,19 @@
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AI14" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
+      <c r="AK14" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>76</v>
@@ -3026,10 +3025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>76</v>
@@ -3039,29 +3038,29 @@
         <v>77</v>
       </c>
       <c r="F15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K15" t="s" s="2">
         <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O15" t="s" s="2">
         <v>76</v>
@@ -3110,7 +3109,7 @@
         <v>76</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>77</v>
@@ -3119,22 +3118,22 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AI15" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
+      <c r="AK15" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>153</v>
       </c>
     </row>
     <row r="16">
@@ -3150,7 +3149,7 @@
         <v>77</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>76</v>
@@ -3225,7 +3224,7 @@
         <v>77</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>76</v>
@@ -3252,7 +3251,7 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3271,16 +3270,16 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
@@ -3327,7 +3326,7 @@
         <v>76</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AE17" t="s" s="2">
         <v>179</v>
@@ -3342,7 +3341,7 @@
         <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>76</v>
@@ -3370,19 +3369,19 @@
         <v>77</v>
       </c>
       <c r="F18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H18" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H18" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>181</v>
@@ -3449,16 +3448,16 @@
         <v>77</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>189</v>
@@ -3483,16 +3482,16 @@
         <v>77</v>
       </c>
       <c r="F19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I19" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>191</v>
@@ -3562,13 +3561,13 @@
         <v>77</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>200</v>
@@ -3593,22 +3592,22 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="F20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>202</v>
@@ -3675,13 +3674,13 @@
         <v>77</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>209</v>
@@ -3706,19 +3705,19 @@
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I21" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>170</v>
@@ -3786,13 +3785,13 @@
         <v>77</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>218</v>
@@ -3820,16 +3819,16 @@
         <v>77</v>
       </c>
       <c r="F22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>222</v>
@@ -3895,13 +3894,13 @@
         <v>77</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>226</v>
@@ -3929,16 +3928,16 @@
         <v>77</v>
       </c>
       <c r="F23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>230</v>
@@ -4006,13 +4005,13 @@
         <v>77</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>235</v>
@@ -4029,7 +4028,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>238</v>
@@ -4042,7 +4041,7 @@
         <v>77</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>76</v>
@@ -4060,11 +4059,11 @@
         <v>240</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O24" t="s" s="2">
         <v>76</v>
@@ -4113,7 +4112,7 @@
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>77</v>
@@ -4122,19 +4121,19 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AI24" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
+      <c r="AK24" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AL24" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>76</v>
@@ -4142,7 +4141,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>241</v>
@@ -4155,29 +4154,29 @@
         <v>77</v>
       </c>
       <c r="F25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I25" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J25" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>76</v>
@@ -4226,7 +4225,7 @@
         <v>76</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>77</v>
@@ -4235,22 +4234,22 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AI25" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
+      <c r="AK25" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>153</v>
       </c>
     </row>
     <row r="26">
@@ -4266,7 +4265,7 @@
         <v>77</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>76</v>
@@ -4341,7 +4340,7 @@
         <v>77</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>76</v>
@@ -4368,7 +4367,7 @@
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -4387,16 +4386,16 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K27" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>176</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
@@ -4443,7 +4442,7 @@
         <v>76</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AE27" t="s" s="2">
         <v>179</v>
@@ -4458,7 +4457,7 @@
         <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>76</v>
@@ -4486,19 +4485,19 @@
         <v>77</v>
       </c>
       <c r="F28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H28" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="I28" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>181</v>
@@ -4565,16 +4564,16 @@
         <v>77</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>189</v>
@@ -4599,16 +4598,16 @@
         <v>77</v>
       </c>
       <c r="F29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I29" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>191</v>
@@ -4678,13 +4677,13 @@
         <v>77</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>200</v>
@@ -4709,22 +4708,22 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I30" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="F30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J30" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>202</v>
@@ -4791,13 +4790,13 @@
         <v>77</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>209</v>
@@ -4822,19 +4821,19 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I31" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F31" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>170</v>
@@ -4900,13 +4899,13 @@
         <v>77</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>218</v>
@@ -4934,16 +4933,16 @@
         <v>77</v>
       </c>
       <c r="F32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>222</v>
@@ -5009,13 +5008,13 @@
         <v>77</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>226</v>
@@ -5043,16 +5042,16 @@
         <v>77</v>
       </c>
       <c r="F33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>230</v>
@@ -5120,13 +5119,13 @@
         <v>77</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>235</v>
@@ -5143,7 +5142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>245</v>
@@ -5156,29 +5155,29 @@
         <v>77</v>
       </c>
       <c r="F34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J34" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>246</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O34" t="s" s="2">
         <v>76</v>
@@ -5227,7 +5226,7 @@
         <v>76</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>77</v>
@@ -5236,22 +5235,22 @@
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AI34" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
+      <c r="AK34" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AK34" t="s" s="2">
+      <c r="AL34" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>153</v>
       </c>
     </row>
     <row r="35">
@@ -5267,7 +5266,7 @@
         <v>77</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>76</v>
@@ -5342,7 +5341,7 @@
         <v>77</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>76</v>
@@ -5369,7 +5368,7 @@
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5388,16 +5387,16 @@
         <v>76</v>
       </c>
       <c r="J36" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K36" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>176</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
@@ -5444,7 +5443,7 @@
         <v>76</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AE36" t="s" s="2">
         <v>179</v>
@@ -5459,7 +5458,7 @@
         <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>76</v>
@@ -5487,19 +5486,19 @@
         <v>77</v>
       </c>
       <c r="F37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H37" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G37" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="I37" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>181</v>
@@ -5566,16 +5565,16 @@
         <v>77</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>189</v>
@@ -5600,16 +5599,16 @@
         <v>77</v>
       </c>
       <c r="F38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>191</v>
@@ -5679,13 +5678,13 @@
         <v>77</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>200</v>
@@ -5710,22 +5709,22 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I39" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="F39" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="J39" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>202</v>
@@ -5792,13 +5791,13 @@
         <v>77</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>209</v>
@@ -5823,19 +5822,19 @@
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I40" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
         <v>170</v>
@@ -5903,13 +5902,13 @@
         <v>77</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>218</v>
@@ -5937,16 +5936,16 @@
         <v>77</v>
       </c>
       <c r="F41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>222</v>
@@ -6012,13 +6011,13 @@
         <v>77</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>226</v>
@@ -6046,16 +6045,16 @@
         <v>77</v>
       </c>
       <c r="F42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>230</v>
@@ -6123,13 +6122,13 @@
         <v>77</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>235</v>
@@ -6157,16 +6156,16 @@
         <v>77</v>
       </c>
       <c r="F43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H43" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="I43" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>249</v>
@@ -6238,13 +6237,13 @@
         <v>77</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>255</v>
@@ -6281,7 +6280,7 @@
         <v>76</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>191</v>
@@ -6321,7 +6320,7 @@
         <v>76</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X44" s="2"/>
       <c r="Y44" t="s" s="2">
@@ -6355,7 +6354,7 @@
         <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>265</v>
@@ -6383,16 +6382,16 @@
         <v>77</v>
       </c>
       <c r="F45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>170</v>
@@ -6462,13 +6461,13 @@
         <v>77</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>273</v>
@@ -6581,7 +6580,7 @@
         <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>76</v>
@@ -6835,16 +6834,16 @@
         <v>77</v>
       </c>
       <c r="F49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I49" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>230</v>
@@ -6912,13 +6911,13 @@
         <v>77</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>255</v>
@@ -7031,7 +7030,7 @@
         <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>76</v>
@@ -7059,7 +7058,7 @@
         <v>77</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>76</v>
@@ -7134,7 +7133,7 @@
         <v>77</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>76</v>
@@ -7161,7 +7160,7 @@
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7180,16 +7179,16 @@
         <v>76</v>
       </c>
       <c r="J52" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>176</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
@@ -7251,7 +7250,7 @@
         <v>76</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>76</v>
@@ -7285,13 +7284,13 @@
         <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>319</v>
@@ -7300,10 +7299,10 @@
         <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>76</v>
@@ -7364,13 +7363,13 @@
         <v>76</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7392,7 +7391,7 @@
         <v>77</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>76</v>
@@ -7469,13 +7468,13 @@
         <v>77</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>76</v>
@@ -7503,7 +7502,7 @@
         <v>77</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>76</v>
@@ -7580,13 +7579,13 @@
         <v>77</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>334</v>
@@ -7697,7 +7696,7 @@
         <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>340</v>
@@ -7725,7 +7724,7 @@
         <v>77</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>76</v>
@@ -7802,13 +7801,13 @@
         <v>77</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>346</v>
@@ -7919,7 +7918,7 @@
         <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-11T09:25:49+00:00</t>
+    <t>2022-10-21T11:28:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:28:25+00:00</t>
+    <t>2022-10-21T11:53:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-21T11:53:19+00:00</t>
+    <t>2022-10-24T14:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T14:23:47+00:00</t>
+    <t>2022-10-24T22:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-24T22:55:30+00:00</t>
+    <t>2022-11-07T08:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T08:18:22+00:00</t>
+    <t>2022-11-07T15:10:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-07T15:10:04+00:00</t>
+    <t>2022-11-08T22:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:20:55+00:00</t>
+    <t>2022-11-08T22:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-08T22:23:46+00:00</t>
+    <t>2022-11-30T21:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-11-30T21:48:52+00:00</t>
+    <t>2022-12-01T00:22:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T00:22:19+00:00</t>
+    <t>2022-12-01T21:15:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-01T21:15:09+00:00</t>
+    <t>2022-12-05T08:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:13:32+00:00</t>
+    <t>2022-12-05T08:52:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:52:10+00:00</t>
+    <t>2022-12-05T08:58:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-12-05T08:58:17+00:00</t>
+    <t>2022-12-05T09:15:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-18T12:02:45+00:00</t>
+    <t>2023-04-24T21:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-24T21:40:58+00:00</t>
+    <t>2023-04-25T17:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-25T17:34:53+00:00</t>
+    <t>2023-04-30T20:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T20:59:20+00:00</t>
+    <t>2023-04-30T21:23:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T21:23:00+00:00</t>
+    <t>2023-05-05T00:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>3.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T00:02:52+00:00</t>
+    <t>2023-11-28T12:13:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,6 +263,10 @@
   </si>
   <si>
     <t>A formally or informally recognized grouping of people or organizations formed for the purpose of achieving some form of collective action.  Includes companies, institutions, corporations, departments, community groups, healthcare practice groups, payer/insurer, etc.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}org-1:The organization SHALL at least have a name or an identifier, and possibly more than one {(identifier.count() + name.count()) &gt; 0}dk-core-organization-mandatory-identifier:Minimum one identifier shall be of type SOR-ID, KOMBIT-ORG-ID or CVR-ID {identifier.where(system='urn:oid:1.2.208.176.1.1' or system='https://kombit.dk/sts/organisation' or system='urn:oid:2.16.840.1.113883.2.24.1.1').exists()}</t>
   </si>
   <si>
     <t>(also see master files messages)</t>
@@ -1335,10 +1339,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1778,13 +1782,13 @@
         <v>77</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>30</v>
@@ -1795,10 +1799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1809,7 +1813,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1818,19 +1822,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1880,13 +1884,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1909,10 +1913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1923,7 +1927,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -1932,16 +1936,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1992,19 +1996,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2021,10 +2025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2035,28 +2039,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2106,19 +2110,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2135,10 +2139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2149,7 +2153,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2161,16 +2165,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2196,13 +2200,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2220,19 +2224,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2249,21 +2253,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2275,16 +2279,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2334,25 +2338,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2363,14 +2367,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2389,16 +2393,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2448,7 +2452,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2466,7 +2470,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2477,14 +2481,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2503,16 +2507,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2562,7 +2566,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2574,13 +2578,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2591,14 +2595,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2611,25 +2615,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2678,7 +2682,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2690,13 +2694,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2707,10 +2711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2718,7 +2722,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -2730,20 +2734,20 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2780,17 +2784,17 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2799,33 +2803,33 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
@@ -2835,7 +2839,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2847,17 +2851,17 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2906,7 +2910,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2915,19 +2919,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2935,13 +2939,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -2951,7 +2955,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -2963,17 +2967,17 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3022,7 +3026,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3031,19 +3035,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3051,13 +3055,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
@@ -3067,7 +3071,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3079,17 +3083,17 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3138,7 +3142,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3147,19 +3151,19 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -3167,13 +3171,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>77</v>
@@ -3183,7 +3187,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3192,20 +3196,20 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3254,7 +3258,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3263,30 +3267,30 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3297,7 +3301,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3309,13 +3313,13 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3366,13 +3370,13 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
@@ -3384,7 +3388,7 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3395,14 +3399,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3421,16 +3425,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3468,19 +3472,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3492,13 +3496,13 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3509,10 +3513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3523,31 +3527,31 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3572,13 +3576,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3596,25 +3600,25 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3625,10 +3629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3639,7 +3643,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3648,22 +3652,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3688,13 +3692,13 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
@@ -3712,25 +3716,25 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3741,10 +3745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3752,10 +3756,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3764,35 +3768,35 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>77</v>
@@ -3828,28 +3832,28 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3857,10 +3861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3868,10 +3872,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -3880,19 +3884,19 @@
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3906,7 +3910,7 @@
         <v>77</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U21" t="s" s="2">
         <v>77</v>
@@ -3942,28 +3946,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3971,10 +3975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3985,7 +3989,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -3994,16 +3998,16 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4054,28 +4058,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4083,10 +4087,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4097,7 +4101,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4106,19 +4110,19 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4168,28 +4172,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4197,13 +4201,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4213,7 +4217,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4225,17 +4229,17 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4284,7 +4288,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4293,19 +4297,19 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4313,13 +4317,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>77</v>
@@ -4329,7 +4333,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4338,20 +4342,20 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4400,7 +4404,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4409,30 +4413,30 @@
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4443,7 +4447,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4455,13 +4459,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4512,13 +4516,13 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4530,7 +4534,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4541,14 +4545,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4567,16 +4571,16 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4614,19 +4618,19 @@
         <v>77</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4638,13 +4642,13 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4655,10 +4659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4669,31 +4673,31 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4718,13 +4722,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4742,25 +4746,25 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4771,10 +4775,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4785,7 +4789,7 @@
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4794,22 +4798,22 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4834,13 +4838,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4858,25 +4862,25 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4887,10 +4891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4898,10 +4902,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4910,35 +4914,35 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>77</v>
@@ -4974,28 +4978,28 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5003,10 +5007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5014,10 +5018,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5026,19 +5030,19 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5052,7 +5056,7 @@
         <v>77</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>77</v>
@@ -5064,11 +5068,11 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5086,28 +5090,28 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5115,10 +5119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5129,7 +5133,7 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5138,16 +5142,16 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5198,28 +5202,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5227,10 +5231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5241,7 +5245,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5250,19 +5254,19 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5312,28 +5316,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5341,13 +5345,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
@@ -5357,7 +5361,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5366,20 +5370,20 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5428,7 +5432,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5437,30 +5441,30 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5471,7 +5475,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5483,13 +5487,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5540,13 +5544,13 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -5558,7 +5562,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5569,14 +5573,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5595,16 +5599,16 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5642,19 +5646,19 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5666,13 +5670,13 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5683,10 +5687,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5697,31 +5701,31 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5746,13 +5750,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5770,25 +5774,25 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5799,10 +5803,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5813,7 +5817,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5822,22 +5826,22 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5862,13 +5866,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -5886,25 +5890,25 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5915,10 +5919,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5926,10 +5930,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -5938,35 +5942,35 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6002,28 +6006,28 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6031,10 +6035,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6042,10 +6046,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6054,19 +6058,19 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6080,7 +6084,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6116,28 +6120,28 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6145,10 +6149,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6159,7 +6163,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6168,16 +6172,16 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6228,28 +6232,28 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6257,10 +6261,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6271,7 +6275,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6280,19 +6284,19 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6342,28 +6346,28 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6371,10 +6375,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6385,114 +6389,114 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q43" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="R43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="J43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q43" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="R43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>86</v>
-      </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6512,22 +6516,22 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6552,11 +6556,11 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6574,7 +6578,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6586,27 +6590,27 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6617,7 +6621,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6626,22 +6630,22 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6690,28 +6694,28 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6719,10 +6723,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6745,19 +6749,19 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6806,7 +6810,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6818,13 +6822,13 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6835,10 +6839,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6861,19 +6865,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6922,7 +6926,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6931,19 +6935,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -6951,10 +6955,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6977,19 +6981,19 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7038,7 +7042,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7047,19 +7051,19 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7067,10 +7071,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7081,7 +7085,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7090,20 +7094,20 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7152,28 +7156,28 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7181,10 +7185,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7207,19 +7211,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7268,7 +7272,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7280,13 +7284,13 @@
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7297,10 +7301,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7311,7 +7315,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7323,13 +7327,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7380,13 +7384,13 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
@@ -7398,7 +7402,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7409,14 +7413,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7435,16 +7439,16 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7494,7 +7498,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7506,13 +7510,13 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7523,14 +7527,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7543,25 +7547,25 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7610,7 +7614,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7622,13 +7626,13 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7639,10 +7643,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7653,7 +7657,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7665,17 +7669,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7700,13 +7704,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7724,25 +7728,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7753,10 +7757,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7767,7 +7771,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7779,17 +7783,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7838,25 +7842,25 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7867,10 +7871,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7893,17 +7897,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7952,7 +7956,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7964,13 +7968,13 @@
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7981,10 +7985,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7995,7 +7999,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8007,17 +8011,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8066,25 +8070,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8095,10 +8099,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8121,17 +8125,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8180,7 +8184,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8192,13 +8196,13 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:13:03+00:00</t>
+    <t>2023-11-30T13:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T13:40:49+00:00</t>
+    <t>2023-11-30T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-30T14:55:40+00:00</t>
+    <t>2023-12-01T12:31:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T12:31:40+00:00</t>
+    <t>2023-12-01T13:42:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-01T13:42:49+00:00</t>
+    <t>2023-12-19T10:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:28:26+00:00</t>
+    <t>2023-12-19T10:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:34:37+00:00</t>
+    <t>2024-01-06T18:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-06T18:57:36+00:00</t>
+    <t>2024-01-08T22:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:06+00:00</t>
+    <t>2024-01-08T22:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="391">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-08T22:02:40+00:00</t>
+    <t>2024-03-19T10:43:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -887,6 +887,19 @@
   </si>
   <si>
     <t>Organization.identifier:Regionskode.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ProducentID</t>
+  </si>
+  <si>
+    <t>ProducentID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-producent-id}
+</t>
+  </si>
+  <si>
+    <t>[DA] Producent Id</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -1519,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.6015625" customWidth="true" bestFit="true"/>
@@ -6378,9 +6391,11 @@
         <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6395,32 +6410,28 @@
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6464,39 +6475,39 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>144</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>290</v>
+        <v>163</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6507,36 +6518,38 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="R44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6556,11 +6569,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6578,13 +6593,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6593,24 +6608,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6621,7 +6636,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6633,19 +6648,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6670,13 +6685,11 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>302</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6694,39 +6707,39 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>309</v>
+        <v>182</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>77</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6737,7 +6750,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6746,22 +6759,22 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>178</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6810,28 +6823,28 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6839,10 +6852,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6865,19 +6878,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6926,7 +6939,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6935,19 +6948,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>322</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -6955,10 +6968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6981,19 +6994,19 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7042,7 +7055,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7051,19 +7064,19 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7071,10 +7084,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7085,7 +7098,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7094,20 +7107,22 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>245</v>
+        <v>331</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7156,28 +7171,28 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>182</v>
+        <v>340</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7185,10 +7200,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7199,7 +7214,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7208,22 +7223,20 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7272,13 +7285,13 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7287,13 +7300,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7301,10 +7314,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7315,7 +7328,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7327,16 +7340,20 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>178</v>
+        <v>347</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>179</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7384,25 +7401,25 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>181</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>182</v>
+        <v>352</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7413,21 +7430,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7439,17 +7456,15 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7498,19 +7513,19 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7527,14 +7542,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>352</v>
+        <v>132</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7547,26 +7562,24 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>353</v>
+        <v>134</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7614,7 +7627,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>355</v>
+        <v>188</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7632,7 +7645,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7643,33 +7656,33 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>77</v>
+        <v>356</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>357</v>
@@ -7677,9 +7690,11 @@
       <c r="M54" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>359</v>
+        <v>142</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7704,13 +7719,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7728,25 +7743,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>362</v>
+        <v>130</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7757,10 +7772,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7783,17 +7798,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>364</v>
+        <v>202</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7818,13 +7833,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7842,7 +7857,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7857,10 +7872,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7871,10 +7886,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7885,7 +7900,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -7897,17 +7912,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7956,13 +7971,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -7971,10 +7986,10 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7985,10 +8000,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7999,7 +8014,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8011,17 +8026,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8070,13 +8085,13 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -8085,10 +8100,10 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8099,10 +8114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8113,7 +8128,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8125,17 +8140,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>383</v>
+        <v>331</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8184,13 +8199,13 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8199,15 +8214,129 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AM59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-19T10:43:29+00:00</t>
+    <t>2024-04-03T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:46:18+00:00</t>
+    <t>2024-04-03T10:16:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -887,19 +887,6 @@
   </si>
   <si>
     <t>Organization.identifier:Regionskode.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier:ProducentID</t>
-  </si>
-  <si>
-    <t>ProducentID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-producent-id}
-</t>
-  </si>
-  <si>
-    <t>[DA] Producent Id</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -1532,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN59"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.6015625" customWidth="true" bestFit="true"/>
@@ -6391,11 +6378,9 @@
         <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6410,28 +6395,32 @@
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N43" s="2"/>
+      <c r="N43" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>148</v>
+        <v>287</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="R43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6475,39 +6464,39 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>144</v>
+        <v>282</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>162</v>
+        <v>289</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>163</v>
+        <v>290</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>164</v>
+        <v>291</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6518,38 +6507,36 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q44" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6569,13 +6556,11 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6593,13 +6578,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6608,24 +6593,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>295</v>
+        <v>182</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6636,7 +6621,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6648,19 +6633,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6685,61 +6670,63 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>182</v>
+        <v>309</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6750,7 +6737,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6759,22 +6746,22 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>178</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6823,28 +6810,28 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6852,10 +6839,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6878,19 +6865,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>178</v>
+        <v>316</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6939,7 +6926,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6948,19 +6935,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>322</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>77</v>
+        <v>323</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -6968,10 +6955,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6994,19 +6981,19 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7055,7 +7042,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7064,19 +7051,19 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7084,10 +7071,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7098,7 +7085,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7107,22 +7094,20 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>331</v>
+        <v>245</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7171,28 +7156,28 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>336</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>337</v>
+        <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>340</v>
+        <v>182</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7200,10 +7185,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7214,7 +7199,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7223,20 +7208,22 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>245</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7285,13 +7272,13 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7300,13 +7287,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7314,10 +7301,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7328,7 +7315,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7340,20 +7327,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>347</v>
+        <v>178</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>348</v>
+        <v>179</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7401,25 +7384,25 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>346</v>
+        <v>181</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>352</v>
+        <v>182</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7430,21 +7413,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7456,15 +7439,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7513,19 +7498,19 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7542,14 +7527,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>132</v>
+        <v>352</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7562,24 +7547,26 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>134</v>
+        <v>353</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>185</v>
+        <v>354</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7627,7 +7614,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>188</v>
+        <v>355</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7645,7 +7632,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7656,33 +7643,33 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>357</v>
@@ -7690,11 +7677,9 @@
       <c r="M54" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N54" t="s" s="2">
-        <v>136</v>
-      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>142</v>
+        <v>359</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7719,13 +7704,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7743,25 +7728,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>130</v>
+        <v>362</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7772,10 +7757,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7798,17 +7783,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>202</v>
+        <v>364</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7833,13 +7818,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7857,7 +7842,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7872,10 +7857,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7886,10 +7871,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7900,7 +7885,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -7912,17 +7897,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>368</v>
+        <v>316</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7971,13 +7956,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -7986,10 +7971,10 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8000,10 +7985,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8014,7 +7999,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8026,17 +8011,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8085,13 +8070,13 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -8100,10 +8085,10 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8114,10 +8099,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8128,7 +8113,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8140,17 +8125,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8199,13 +8184,13 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8214,129 +8199,15 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>385</v>
+        <v>182</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN59" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="391">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T10:16:02+00:00</t>
+    <t>2024-04-10T06:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Denmark (http://www.hl7.dk, jenskristianvilladsen@gmail.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -887,6 +887,19 @@
   </si>
   <si>
     <t>Organization.identifier:Regionskode.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:ProducentID</t>
+  </si>
+  <si>
+    <t>ProducentID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://hl7.dk/fhir/core/StructureDefinition/dk-core-producent-id}
+</t>
+  </si>
+  <si>
+    <t>[DA] Producent Id</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -1519,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.6015625" customWidth="true" bestFit="true"/>
@@ -6378,9 +6391,11 @@
         <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6395,32 +6410,28 @@
         <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>288</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6464,39 +6475,39 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>282</v>
+        <v>144</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>289</v>
+        <v>162</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>290</v>
+        <v>163</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6507,36 +6518,38 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="R44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6556,11 +6569,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6578,13 +6593,13 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
@@ -6593,24 +6608,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6621,7 +6636,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6633,19 +6648,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6670,13 +6685,11 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>302</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6694,39 +6707,39 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>309</v>
+        <v>182</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>77</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6737,7 +6750,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6746,22 +6759,22 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>178</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6810,28 +6823,28 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6839,10 +6852,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6865,19 +6878,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6926,7 +6939,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6935,19 +6948,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>322</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>325</v>
+        <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -6955,10 +6968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6981,19 +6994,19 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7042,7 +7055,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7051,19 +7064,19 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7071,10 +7084,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7085,7 +7098,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7094,20 +7107,22 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>245</v>
+        <v>331</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7156,28 +7171,28 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="AK49" t="s" s="2">
-        <v>289</v>
+        <v>338</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>182</v>
+        <v>340</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7185,10 +7200,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7199,7 +7214,7 @@
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7208,22 +7223,20 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7272,13 +7285,13 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
@@ -7287,13 +7300,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7301,10 +7314,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7315,7 +7328,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7327,16 +7340,20 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>178</v>
+        <v>347</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>179</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7384,25 +7401,25 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>181</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>182</v>
+        <v>352</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7413,21 +7430,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7439,17 +7456,15 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7498,19 +7513,19 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7527,14 +7542,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>352</v>
+        <v>132</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7547,26 +7562,24 @@
         <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>353</v>
+        <v>134</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>354</v>
+        <v>185</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7614,7 +7627,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>355</v>
+        <v>188</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7632,7 +7645,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7643,33 +7656,33 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>77</v>
+        <v>356</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>357</v>
@@ -7677,9 +7690,11 @@
       <c r="M54" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N54" s="2"/>
+      <c r="N54" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>359</v>
+        <v>142</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7704,13 +7719,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -7728,25 +7743,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>362</v>
+        <v>130</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7757,10 +7772,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7783,17 +7798,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>364</v>
+        <v>202</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7818,13 +7833,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7842,7 +7857,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7857,10 +7872,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7871,10 +7886,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7885,7 +7900,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -7897,17 +7912,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7956,13 +7971,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -7971,10 +7986,10 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7985,10 +8000,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7999,7 +8014,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8011,17 +8026,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8070,13 +8085,13 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
@@ -8085,10 +8100,10 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8099,10 +8114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8113,7 +8128,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8125,17 +8140,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>383</v>
+        <v>331</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8184,13 +8199,13 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8199,15 +8214,129 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AM59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T06:34:41+00:00</t>
+    <t>2024-04-11T09:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-11T09:53:59+00:00</t>
+    <t>2024-04-12T06:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T06:23:14+00:00</t>
+    <t>2024-04-16T10:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-16T10:58:26+00:00</t>
+    <t>2024-04-18T15:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:20:26+00:00</t>
+    <t>2024-04-18T15:27:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T15:27:51+00:00</t>
+    <t>2024-04-22T11:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T11:01:11+00:00</t>
+    <t>2024-04-22T12:03:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T12:03:36+00:00</t>
+    <t>2024-04-22T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T13:38:01+00:00</t>
+    <t>2024-04-23T08:24:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T08:24:27+00:00</t>
+    <t>2024-04-23T10:50:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T10:50:14+00:00</t>
+    <t>2024-04-23T18:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T18:15:55+00:00</t>
+    <t>2024-05-02T12:47:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T12:47:39+00:00</t>
+    <t>2024-05-03T13:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T13:03:24+00:00</t>
+    <t>2024-05-06T06:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T06:35:09+00:00</t>
+    <t>2024-05-06T07:49:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T07:49:19+00:00</t>
+    <t>2024-05-06T14:14:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T14:14:33+00:00</t>
+    <t>2024-05-10T08:40:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:41:58+00:00</t>
+    <t>2024-05-12T09:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T09:45:49+00:00</t>
+    <t>2024-05-12T11:37:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T11:37:02+00:00</t>
+    <t>2024-06-03T20:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T20:51:53+00:00</t>
+    <t>2024-06-25T21:12:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:12:58+00:00</t>
+    <t>2024-10-17T12:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T12:15:17+00:00</t>
+    <t>2024-10-18T06:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.4.0</t>
+    <t>3.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:45:46+00:00</t>
+    <t>2024-11-15T12:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T12:49:28+00:00</t>
+    <t>2024-11-15T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T13:03:47+00:00</t>
+    <t>2024-11-29T07:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T07:41:39+00:00</t>
+    <t>2024-11-29T10:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-29T10:20:07+00:00</t>
+    <t>2024-12-11T08:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:38:49+00:00</t>
+    <t>2024-12-11T09:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T09:50:58+00:00</t>
+    <t>2024-12-16T15:09:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:09:03+00:00</t>
+    <t>2024-12-16T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-organization.xlsx
+++ b/StructureDefinition-dk-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T15:16:17+00:00</t>
+    <t>2024-12-16T15:31:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
